--- a/data/Low_Price.xlsx
+++ b/data/Low_Price.xlsx
@@ -485,7 +485,7 @@
         <v>42.49</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>37.69</v>
+        <v>40.05</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>37.24</v>
@@ -536,7 +536,7 @@
         <v>22.15</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>21.78</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="7">
@@ -568,7 +568,7 @@
         <v>29.8</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>28.51</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="9">
@@ -805,7 +805,7 @@
         <v>140.75</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>136</v>
+        <v>137.01</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>130</v>
@@ -904,7 +904,7 @@
         <v>25475</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>25135</v>
+        <v>25475</v>
       </c>
     </row>
     <row r="30">
@@ -952,7 +952,7 @@
         <v>680.85</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>599</v>
+        <v>619</v>
       </c>
     </row>
     <row r="33">
@@ -1221,7 +1221,7 @@
         <v>4.13</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>3.97</v>
@@ -1240,7 +1240,7 @@
         <v>1163.2</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1086.1</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="51">
@@ -1320,7 +1320,7 @@
         <v>406</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>389.6</v>
+        <v>402.15</v>
       </c>
     </row>
     <row r="56">
@@ -1749,7 +1749,7 @@
         <v>218.75</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>208.4</v>
+        <v>211.9</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>189.8</v>
@@ -1829,7 +1829,7 @@
         <v>8.09</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>6.95</v>
+        <v>7.35</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>6.95</v>
@@ -1941,7 +1941,7 @@
         <v>94.03</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>86.15000000000001</v>
+        <v>88</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>85.55</v>
@@ -1976,7 +1976,7 @@
         <v>25.51</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>17.54</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="97">
@@ -1989,7 +1989,7 @@
         <v>37.47</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>35.75</v>
+        <v>36</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>32.7</v>
@@ -2072,7 +2072,7 @@
         <v>536.85</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>503</v>
+        <v>518.05</v>
       </c>
     </row>
     <row r="103">
@@ -2456,7 +2456,7 @@
         <v>5172</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>5051</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="127">
@@ -2501,7 +2501,7 @@
         <v>848</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>768.65</v>
+        <v>774</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>741.3</v>
@@ -2549,7 +2549,7 @@
         <v>8.99</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>7.95</v>
+        <v>8.24</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>6.92</v>
@@ -2677,7 +2677,7 @@
         <v>622.1</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>609.7</v>
+        <v>616</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>477.3</v>
@@ -2709,7 +2709,7 @@
         <v>936</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>753.7</v>
+        <v>756.1</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>636.05</v>
@@ -2757,7 +2757,7 @@
         <v>38.5</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>38.11</v>
+        <v>38.3</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>36.7</v>
@@ -3061,7 +3061,7 @@
         <v>45.85</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>43.84</v>
+        <v>45.05</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>43.22</v>
@@ -3272,7 +3272,7 @@
         <v>10.98</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>10.74</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="178">
@@ -3605,7 +3605,7 @@
         <v>106.45</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>97.7</v>
+        <v>102.28</v>
       </c>
       <c r="D198" s="2" t="n">
         <v>80.84</v>
@@ -3624,7 +3624,7 @@
         <v>465.5</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>445.2</v>
+        <v>453</v>
       </c>
     </row>
     <row r="200">
@@ -3653,10 +3653,10 @@
         <v>96.5</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>93.43000000000001</v>
+        <v>93.53</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>74.52</v>
+        <v>79.13</v>
       </c>
     </row>
     <row r="202">
@@ -3768,7 +3768,7 @@
         <v>812.05</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>780</v>
+        <v>812.05</v>
       </c>
     </row>
     <row r="209">
@@ -4072,7 +4072,7 @@
         <v>14.1</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>14.01</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="228">
@@ -4293,7 +4293,7 @@
         <v>1442</v>
       </c>
       <c r="C241" s="2" t="n">
-        <v>1390.2</v>
+        <v>1405</v>
       </c>
       <c r="D241" s="2" t="n">
         <v>1316.1</v>
@@ -4421,7 +4421,7 @@
         <v>26.7</v>
       </c>
       <c r="C249" s="2" t="n">
-        <v>24.24</v>
+        <v>24.32</v>
       </c>
       <c r="D249" s="2" t="n">
         <v>23.1</v>
@@ -4533,7 +4533,7 @@
         <v>1300.1</v>
       </c>
       <c r="C256" s="2" t="n">
-        <v>1137.5</v>
+        <v>1210.1</v>
       </c>
       <c r="D256" s="2" t="n">
         <v>806.05</v>
@@ -4629,7 +4629,7 @@
         <v>155.88</v>
       </c>
       <c r="C262" s="2" t="n">
-        <v>131.33</v>
+        <v>135.41</v>
       </c>
       <c r="D262" s="2" t="n">
         <v>131.33</v>
@@ -4725,7 +4725,7 @@
         <v>995</v>
       </c>
       <c r="C268" s="2" t="n">
-        <v>880.1</v>
+        <v>916.2</v>
       </c>
       <c r="D268" s="2" t="n">
         <v>708</v>
@@ -4933,7 +4933,7 @@
         <v>1268.4</v>
       </c>
       <c r="C281" s="2" t="n">
-        <v>1230.2</v>
+        <v>1232.6</v>
       </c>
       <c r="D281" s="2" t="n">
         <v>1175</v>
@@ -5221,10 +5221,10 @@
         <v>434.85</v>
       </c>
       <c r="C299" s="2" t="n">
-        <v>401.85</v>
+        <v>409.8</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>301.45</v>
+        <v>301.55</v>
       </c>
     </row>
     <row r="300">
@@ -5557,7 +5557,7 @@
         <v>157.99</v>
       </c>
       <c r="C320" s="2" t="n">
-        <v>154.1</v>
+        <v>154.13</v>
       </c>
       <c r="D320" s="2" t="n">
         <v>149.85</v>
@@ -5765,7 +5765,7 @@
         <v>238.43</v>
       </c>
       <c r="C333" s="2" t="n">
-        <v>230.18</v>
+        <v>233.07</v>
       </c>
       <c r="D333" s="2" t="n">
         <v>223.82</v>
@@ -5861,7 +5861,7 @@
         <v>134.34</v>
       </c>
       <c r="C339" s="2" t="n">
-        <v>130.26</v>
+        <v>131.9</v>
       </c>
       <c r="D339" s="2" t="n">
         <v>126.73</v>
@@ -5893,7 +5893,7 @@
         <v>82.01000000000001</v>
       </c>
       <c r="C341" s="2" t="n">
-        <v>78.58</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="D341" s="2" t="n">
         <v>78.5</v>
@@ -6085,7 +6085,7 @@
         <v>921.2</v>
       </c>
       <c r="C353" s="2" t="n">
-        <v>815.85</v>
+        <v>851.2</v>
       </c>
       <c r="D353" s="2" t="n">
         <v>727.1</v>
@@ -6245,7 +6245,7 @@
         <v>108.5</v>
       </c>
       <c r="C363" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D363" s="2" t="n">
         <v>98.2</v>
@@ -6293,7 +6293,7 @@
         <v>248.1</v>
       </c>
       <c r="C366" s="2" t="n">
-        <v>239.13</v>
+        <v>243.16</v>
       </c>
       <c r="D366" s="2" t="n">
         <v>237</v>
@@ -6485,7 +6485,7 @@
         <v>274</v>
       </c>
       <c r="C378" s="2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D378" s="2" t="n">
         <v>218</v>
@@ -6520,7 +6520,7 @@
         <v>358</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>287.95</v>
+        <v>291.5</v>
       </c>
     </row>
     <row r="381">
@@ -6597,7 +6597,7 @@
         <v>102.8</v>
       </c>
       <c r="C385" s="2" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D385" s="2" t="n">
         <v>98.59999999999999</v>
@@ -6677,7 +6677,7 @@
         <v>1535</v>
       </c>
       <c r="C390" s="2" t="n">
-        <v>1376.5</v>
+        <v>1467.9</v>
       </c>
       <c r="D390" s="2" t="n">
         <v>1359.2</v>
@@ -6712,7 +6712,7 @@
         <v>91.15000000000001</v>
       </c>
       <c r="D392" s="2" t="n">
-        <v>87.75</v>
+        <v>91.15000000000001</v>
       </c>
     </row>
     <row r="393">
@@ -6773,10 +6773,10 @@
         <v>4.42</v>
       </c>
       <c r="C396" s="2" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="D396" s="2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
     </row>
     <row r="397">
@@ -6885,7 +6885,7 @@
         <v>1320</v>
       </c>
       <c r="C403" s="2" t="n">
-        <v>1190.3</v>
+        <v>1260.1</v>
       </c>
       <c r="D403" s="2" t="n">
         <v>1190.3</v>
@@ -6965,7 +6965,7 @@
         <v>16.3</v>
       </c>
       <c r="C408" s="2" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="D408" s="2" t="n">
         <v>15.26</v>
@@ -7080,7 +7080,7 @@
         <v>1.89</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="416">
@@ -7272,7 +7272,7 @@
         <v>166.21</v>
       </c>
       <c r="D427" s="2" t="n">
-        <v>157.81</v>
+        <v>166.21</v>
       </c>
     </row>
     <row r="428">
@@ -7461,10 +7461,10 @@
         <v>1884.9</v>
       </c>
       <c r="C439" s="2" t="n">
-        <v>1827.2</v>
+        <v>1830.2</v>
       </c>
       <c r="D439" s="2" t="n">
-        <v>1449.8</v>
+        <v>1499.9</v>
       </c>
     </row>
     <row r="440">
@@ -7573,7 +7573,7 @@
         <v>64</v>
       </c>
       <c r="C446" s="2" t="n">
-        <v>58.5</v>
+        <v>59.01</v>
       </c>
       <c r="D446" s="2" t="n">
         <v>52.97</v>
@@ -7589,7 +7589,7 @@
         <v>3375.4</v>
       </c>
       <c r="C447" s="2" t="n">
-        <v>3246.5</v>
+        <v>3262.8</v>
       </c>
       <c r="D447" s="2" t="n">
         <v>3000</v>
@@ -7637,7 +7637,7 @@
         <v>121.5</v>
       </c>
       <c r="C450" s="2" t="n">
-        <v>119.01</v>
+        <v>119.1</v>
       </c>
       <c r="D450" s="2" t="n">
         <v>115.05</v>
@@ -7893,7 +7893,7 @@
         <v>120.44</v>
       </c>
       <c r="C466" s="2" t="n">
-        <v>116.51</v>
+        <v>117.2</v>
       </c>
       <c r="D466" s="2" t="n">
         <v>116.51</v>
@@ -7989,7 +7989,7 @@
         <v>274.85</v>
       </c>
       <c r="C472" s="2" t="n">
-        <v>263.9</v>
+        <v>264.05</v>
       </c>
       <c r="D472" s="2" t="n">
         <v>262.25</v>
@@ -8021,7 +8021,7 @@
         <v>22.65</v>
       </c>
       <c r="C474" s="2" t="n">
-        <v>20.59</v>
+        <v>22</v>
       </c>
       <c r="D474" s="2" t="n">
         <v>16.9</v>
@@ -8533,7 +8533,7 @@
         <v>134.5</v>
       </c>
       <c r="C506" s="2" t="n">
-        <v>129.1</v>
+        <v>130</v>
       </c>
       <c r="D506" s="2" t="n">
         <v>129.1</v>
@@ -8629,7 +8629,7 @@
         <v>82</v>
       </c>
       <c r="C512" s="2" t="n">
-        <v>78.52</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D512" s="2" t="n">
         <v>76.3</v>
@@ -8693,7 +8693,7 @@
         <v>1459.9</v>
       </c>
       <c r="C516" s="2" t="n">
-        <v>1410</v>
+        <v>1426</v>
       </c>
       <c r="D516" s="2" t="n">
         <v>1325.1</v>
@@ -8853,7 +8853,7 @@
         <v>14.32</v>
       </c>
       <c r="C526" s="2" t="n">
-        <v>13.8</v>
+        <v>14.11</v>
       </c>
       <c r="D526" s="2" t="n">
         <v>13.4</v>
@@ -8968,7 +8968,7 @@
         <v>508.1</v>
       </c>
       <c r="D533" s="2" t="n">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="534">
@@ -9109,7 +9109,7 @@
         <v>31.21</v>
       </c>
       <c r="C542" s="2" t="n">
-        <v>29.71</v>
+        <v>30</v>
       </c>
       <c r="D542" s="2" t="n">
         <v>28.86</v>
@@ -9528,7 +9528,7 @@
         <v>145.7</v>
       </c>
       <c r="D568" s="2" t="n">
-        <v>130.32</v>
+        <v>131.35</v>
       </c>
     </row>
     <row r="569">
@@ -9541,7 +9541,7 @@
         <v>182</v>
       </c>
       <c r="C569" s="2" t="n">
-        <v>175.11</v>
+        <v>177.25</v>
       </c>
       <c r="D569" s="2" t="n">
         <v>170.1</v>
@@ -9656,7 +9656,7 @@
         <v>5.63</v>
       </c>
       <c r="D576" s="2" t="n">
-        <v>5.26</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="577">
@@ -9669,7 +9669,7 @@
         <v>1280</v>
       </c>
       <c r="C577" s="2" t="n">
-        <v>1231.1</v>
+        <v>1231.9</v>
       </c>
       <c r="D577" s="2" t="n">
         <v>1209.1</v>
@@ -9816,7 +9816,7 @@
         <v>87.91</v>
       </c>
       <c r="D586" s="2" t="n">
-        <v>76.26000000000001</v>
+        <v>81.59</v>
       </c>
     </row>
     <row r="587">
@@ -9845,7 +9845,7 @@
         <v>234.5</v>
       </c>
       <c r="C588" s="2" t="n">
-        <v>219.37</v>
+        <v>219.74</v>
       </c>
       <c r="D588" s="2" t="n">
         <v>210.69</v>
@@ -9861,7 +9861,7 @@
         <v>191.31</v>
       </c>
       <c r="C589" s="2" t="n">
-        <v>143.75</v>
+        <v>157.01</v>
       </c>
       <c r="D589" s="2" t="n">
         <v>74.5</v>
@@ -9893,7 +9893,7 @@
         <v>352.25</v>
       </c>
       <c r="C591" s="2" t="n">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D591" s="2" t="n">
         <v>246.45</v>
@@ -9973,7 +9973,7 @@
         <v>1014</v>
       </c>
       <c r="C596" s="2" t="n">
-        <v>935.3</v>
+        <v>941.1</v>
       </c>
       <c r="D596" s="2" t="n">
         <v>811.95</v>
@@ -9992,7 +9992,7 @@
         <v>372.8</v>
       </c>
       <c r="D597" s="2" t="n">
-        <v>372.1</v>
+        <v>372.8</v>
       </c>
     </row>
     <row r="598">
@@ -10136,7 +10136,7 @@
         <v>2.22</v>
       </c>
       <c r="D606" s="2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="607">
@@ -10261,7 +10261,7 @@
         <v>209.32</v>
       </c>
       <c r="C614" s="2" t="n">
-        <v>195.38</v>
+        <v>195.62</v>
       </c>
       <c r="D614" s="2" t="n">
         <v>191.94</v>
@@ -10501,7 +10501,7 @@
         <v>1384</v>
       </c>
       <c r="C629" s="2" t="n">
-        <v>1361.9</v>
+        <v>1365.9</v>
       </c>
       <c r="D629" s="2" t="n">
         <v>1269.1</v>
@@ -10517,7 +10517,7 @@
         <v>1622.5</v>
       </c>
       <c r="C630" s="2" t="n">
-        <v>1536</v>
+        <v>1558.7</v>
       </c>
       <c r="D630" s="2" t="n">
         <v>1473.1</v>
@@ -10741,7 +10741,7 @@
         <v>470</v>
       </c>
       <c r="C644" s="2" t="n">
-        <v>445.7</v>
+        <v>450</v>
       </c>
       <c r="D644" s="2" t="n">
         <v>445</v>
@@ -10773,7 +10773,7 @@
         <v>34.68</v>
       </c>
       <c r="C646" s="2" t="n">
-        <v>28.41</v>
+        <v>31.41</v>
       </c>
       <c r="D646" s="2" t="n">
         <v>26</v>
@@ -10821,7 +10821,7 @@
         <v>4.01</v>
       </c>
       <c r="C649" s="2" t="n">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="D649" s="2" t="n">
         <v>3.56</v>
@@ -10853,7 +10853,7 @@
         <v>21.74</v>
       </c>
       <c r="C651" s="2" t="n">
-        <v>19</v>
+        <v>19.98</v>
       </c>
       <c r="D651" s="2" t="n">
         <v>18.76</v>
@@ -10968,7 +10968,7 @@
         <v>17.5</v>
       </c>
       <c r="D658" s="2" t="n">
-        <v>17.1</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="659">
@@ -11045,7 +11045,7 @@
         <v>11502</v>
       </c>
       <c r="C663" s="2" t="n">
-        <v>11201</v>
+        <v>11211</v>
       </c>
       <c r="D663" s="2" t="n">
         <v>11000</v>
@@ -11349,7 +11349,7 @@
         <v>2290.2</v>
       </c>
       <c r="C682" s="2" t="n">
-        <v>2134.2</v>
+        <v>2150</v>
       </c>
       <c r="D682" s="2" t="n">
         <v>1290</v>
@@ -11464,7 +11464,7 @@
         <v>1167.2</v>
       </c>
       <c r="D689" s="2" t="n">
-        <v>1130</v>
+        <v>1133.9</v>
       </c>
     </row>
     <row r="690">
@@ -11493,10 +11493,10 @@
         <v>29.92</v>
       </c>
       <c r="C691" s="2" t="n">
-        <v>27.66</v>
+        <v>28.21</v>
       </c>
       <c r="D691" s="2" t="n">
-        <v>20.59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="692">
@@ -11624,7 +11624,7 @@
         <v>13111</v>
       </c>
       <c r="D699" s="2" t="n">
-        <v>11250</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="700">
@@ -11637,7 +11637,7 @@
         <v>234.9</v>
       </c>
       <c r="C700" s="2" t="n">
-        <v>217.6</v>
+        <v>220.1</v>
       </c>
       <c r="D700" s="2" t="n">
         <v>217.6</v>
@@ -11701,7 +11701,7 @@
         <v>2.36</v>
       </c>
       <c r="C704" s="2" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="D704" s="2" t="n">
         <v>2.05</v>
@@ -11717,7 +11717,7 @@
         <v>16.12</v>
       </c>
       <c r="C705" s="2" t="n">
-        <v>15.89</v>
+        <v>16</v>
       </c>
       <c r="D705" s="2" t="n">
         <v>15.63</v>
@@ -11765,7 +11765,7 @@
         <v>1439.21</v>
       </c>
       <c r="C708" s="2" t="n">
-        <v>1422.93</v>
+        <v>1424.56</v>
       </c>
       <c r="D708" s="2" t="n">
         <v>1420.61</v>
@@ -12229,7 +12229,7 @@
         <v>1051.77</v>
       </c>
       <c r="C737" s="2" t="n">
-        <v>1050.82</v>
+        <v>1050.84</v>
       </c>
       <c r="D737" s="2" t="n">
         <v>1044.6</v>
@@ -12501,7 +12501,7 @@
         <v>1.99</v>
       </c>
       <c r="C754" s="2" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="D754" s="2" t="n">
         <v>1.47</v>
@@ -12536,7 +12536,7 @@
         <v>535.9</v>
       </c>
       <c r="D756" s="2" t="n">
-        <v>489</v>
+        <v>531</v>
       </c>
     </row>
     <row r="757">
@@ -12757,7 +12757,7 @@
         <v>252.5</v>
       </c>
       <c r="C770" s="2" t="n">
-        <v>245.22</v>
+        <v>249</v>
       </c>
       <c r="D770" s="2" t="n">
         <v>213.22</v>
@@ -12885,7 +12885,7 @@
         <v>1155</v>
       </c>
       <c r="C778" s="2" t="n">
-        <v>1141</v>
+        <v>1142.2</v>
       </c>
       <c r="D778" s="2" t="n">
         <v>1141</v>
@@ -12949,7 +12949,7 @@
         <v>1554</v>
       </c>
       <c r="C782" s="2" t="n">
-        <v>1309</v>
+        <v>1355.6</v>
       </c>
       <c r="D782" s="2" t="n">
         <v>1294.3</v>
@@ -13365,7 +13365,7 @@
         <v>806</v>
       </c>
       <c r="C808" s="2" t="n">
-        <v>680</v>
+        <v>712</v>
       </c>
       <c r="D808" s="2" t="n">
         <v>585.2</v>
@@ -13448,7 +13448,7 @@
         <v>57.79</v>
       </c>
       <c r="D813" s="2" t="n">
-        <v>48.5</v>
+        <v>49.01</v>
       </c>
     </row>
     <row r="814">
@@ -13461,7 +13461,7 @@
         <v>329.5</v>
       </c>
       <c r="C814" s="2" t="n">
-        <v>317.05</v>
+        <v>319.5</v>
       </c>
       <c r="D814" s="2" t="n">
         <v>313.75</v>
@@ -13544,7 +13544,7 @@
         <v>104.7</v>
       </c>
       <c r="D819" s="2" t="n">
-        <v>74.27</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="820">
@@ -13637,7 +13637,7 @@
         <v>135.25</v>
       </c>
       <c r="C825" s="2" t="n">
-        <v>127.24</v>
+        <v>131.54</v>
       </c>
       <c r="D825" s="2" t="n">
         <v>125.01</v>
@@ -13752,7 +13752,7 @@
         <v>3.13</v>
       </c>
       <c r="D832" s="2" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="833">
@@ -13941,7 +13941,7 @@
         <v>1494.6</v>
       </c>
       <c r="C844" s="2" t="n">
-        <v>1403.9</v>
+        <v>1456.6</v>
       </c>
       <c r="D844" s="2" t="n">
         <v>1195.2</v>
@@ -13973,10 +13973,10 @@
         <v>291</v>
       </c>
       <c r="C846" s="2" t="n">
-        <v>257.6</v>
+        <v>260.1</v>
       </c>
       <c r="D846" s="2" t="n">
-        <v>246.65</v>
+        <v>247</v>
       </c>
     </row>
     <row r="847">
@@ -14117,7 +14117,7 @@
         <v>300.9</v>
       </c>
       <c r="C855" s="2" t="n">
-        <v>282.25</v>
+        <v>285.6</v>
       </c>
       <c r="D855" s="2" t="n">
         <v>247.05</v>
@@ -14181,7 +14181,7 @@
         <v>158.6</v>
       </c>
       <c r="C859" s="2" t="n">
-        <v>144.5</v>
+        <v>147.71</v>
       </c>
       <c r="D859" s="2" t="n">
         <v>144.5</v>
@@ -14424,7 +14424,7 @@
         <v>28.3</v>
       </c>
       <c r="D874" s="2" t="n">
-        <v>27.26</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="875">
@@ -14485,7 +14485,7 @@
         <v>10.7</v>
       </c>
       <c r="C878" s="2" t="n">
-        <v>10.07</v>
+        <v>10.1</v>
       </c>
       <c r="D878" s="2" t="n">
         <v>9.25</v>
@@ -14888,7 +14888,7 @@
         <v>139.22</v>
       </c>
       <c r="D903" s="2" t="n">
-        <v>122</v>
+        <v>123.11</v>
       </c>
     </row>
     <row r="904">
@@ -14901,7 +14901,7 @@
         <v>11.8</v>
       </c>
       <c r="C904" s="2" t="n">
-        <v>10.12</v>
+        <v>10.75</v>
       </c>
       <c r="D904" s="2" t="n">
         <v>9.85</v>
@@ -15221,7 +15221,7 @@
         <v>279.25</v>
       </c>
       <c r="C924" s="2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D924" s="2" t="n">
         <v>231.65</v>
@@ -15365,7 +15365,7 @@
         <v>143.25</v>
       </c>
       <c r="C933" s="2" t="n">
-        <v>141.75</v>
+        <v>142.05</v>
       </c>
       <c r="D933" s="2" t="n">
         <v>137.15</v>
@@ -15557,7 +15557,7 @@
         <v>564.45</v>
       </c>
       <c r="C945" s="2" t="n">
-        <v>485</v>
+        <v>492.4</v>
       </c>
       <c r="D945" s="2" t="n">
         <v>475.6</v>
@@ -15957,7 +15957,7 @@
         <v>193.61</v>
       </c>
       <c r="C970" s="2" t="n">
-        <v>189.45</v>
+        <v>189.5</v>
       </c>
       <c r="D970" s="2" t="n">
         <v>178.01</v>
@@ -16069,7 +16069,7 @@
         <v>111.15</v>
       </c>
       <c r="C977" s="2" t="n">
-        <v>111.05</v>
+        <v>111.07</v>
       </c>
       <c r="D977" s="2" t="n">
         <v>110.51</v>
@@ -16245,7 +16245,7 @@
         <v>81.5</v>
       </c>
       <c r="C988" s="2" t="n">
-        <v>79.3</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="D988" s="2" t="n">
         <v>78.67</v>
@@ -16357,7 +16357,7 @@
         <v>7200</v>
       </c>
       <c r="C995" s="2" t="n">
-        <v>6834</v>
+        <v>6834.5</v>
       </c>
       <c r="D995" s="2" t="n">
         <v>6240</v>
@@ -16677,7 +16677,7 @@
         <v>52.11</v>
       </c>
       <c r="C1015" s="2" t="n">
-        <v>40.05</v>
+        <v>40.13</v>
       </c>
       <c r="D1015" s="2" t="n">
         <v>39</v>
@@ -16712,7 +16712,7 @@
         <v>1051</v>
       </c>
       <c r="D1017" s="2" t="n">
-        <v>1010.3</v>
+        <v>1032.8</v>
       </c>
     </row>
     <row r="1018">
@@ -16888,7 +16888,7 @@
         <v>1525.2</v>
       </c>
       <c r="D1028" s="2" t="n">
-        <v>1437</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="1029">
@@ -17221,7 +17221,7 @@
         <v>1326</v>
       </c>
       <c r="C1049" s="2" t="n">
-        <v>1172.8</v>
+        <v>1175</v>
       </c>
       <c r="D1049" s="2" t="n">
         <v>1172.8</v>
@@ -17272,7 +17272,7 @@
         <v>690.5</v>
       </c>
       <c r="D1052" s="2" t="n">
-        <v>681.9</v>
+        <v>690.5</v>
       </c>
     </row>
     <row r="1053">
@@ -17333,7 +17333,7 @@
         <v>560</v>
       </c>
       <c r="C1056" s="2" t="n">
-        <v>538.35</v>
+        <v>542.05</v>
       </c>
       <c r="D1056" s="2" t="n">
         <v>513.4</v>
@@ -17525,7 +17525,7 @@
         <v>27.77</v>
       </c>
       <c r="C1068" s="2" t="n">
-        <v>26.88</v>
+        <v>27.32</v>
       </c>
       <c r="D1068" s="2" t="n">
         <v>26.67</v>
@@ -17621,7 +17621,7 @@
         <v>6.2</v>
       </c>
       <c r="C1074" s="2" t="n">
-        <v>5.76</v>
+        <v>5.95</v>
       </c>
       <c r="D1074" s="2" t="n">
         <v>5.76</v>
@@ -17909,7 +17909,7 @@
         <v>158.2</v>
       </c>
       <c r="C1092" s="2" t="n">
-        <v>153.01</v>
+        <v>154.01</v>
       </c>
       <c r="D1092" s="2" t="n">
         <v>149</v>
@@ -17925,7 +17925,7 @@
         <v>560.55</v>
       </c>
       <c r="C1093" s="2" t="n">
-        <v>495.45</v>
+        <v>503</v>
       </c>
       <c r="D1093" s="2" t="n">
         <v>476.25</v>
@@ -18021,7 +18021,7 @@
         <v>51.75</v>
       </c>
       <c r="C1099" s="2" t="n">
-        <v>44.95</v>
+        <v>46.24</v>
       </c>
       <c r="D1099" s="2" t="n">
         <v>40.1</v>
@@ -18069,10 +18069,10 @@
         <v>382</v>
       </c>
       <c r="C1102" s="2" t="n">
-        <v>370.3</v>
+        <v>373</v>
       </c>
       <c r="D1102" s="2" t="n">
-        <v>345.25</v>
+        <v>354.1</v>
       </c>
     </row>
     <row r="1103">
@@ -18117,7 +18117,7 @@
         <v>440.55</v>
       </c>
       <c r="C1105" s="2" t="n">
-        <v>398.1</v>
+        <v>404.1</v>
       </c>
       <c r="D1105" s="2" t="n">
         <v>365.1</v>
@@ -18165,7 +18165,7 @@
         <v>172.49</v>
       </c>
       <c r="C1108" s="2" t="n">
-        <v>165.81</v>
+        <v>166.31</v>
       </c>
       <c r="D1108" s="2" t="n">
         <v>164.01</v>
@@ -18213,7 +18213,7 @@
         <v>171.87</v>
       </c>
       <c r="C1111" s="2" t="n">
-        <v>166.31</v>
+        <v>166.82</v>
       </c>
       <c r="D1111" s="2" t="n">
         <v>165</v>
@@ -18328,7 +18328,7 @@
         <v>400.8</v>
       </c>
       <c r="D1118" s="2" t="n">
-        <v>363</v>
+        <v>388.05</v>
       </c>
     </row>
     <row r="1119">
@@ -18360,7 +18360,7 @@
         <v>22.68</v>
       </c>
       <c r="D1120" s="2" t="n">
-        <v>19.68</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="1121">
@@ -18597,7 +18597,7 @@
         <v>88.5</v>
       </c>
       <c r="C1135" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="D1135" s="2" t="n">
         <v>62.91</v>
@@ -18725,10 +18725,10 @@
         <v>36.65</v>
       </c>
       <c r="C1143" s="2" t="n">
-        <v>31.2</v>
+        <v>32.78</v>
       </c>
       <c r="D1143" s="2" t="n">
-        <v>24.31</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="1144">
@@ -18757,7 +18757,7 @@
         <v>672.5</v>
       </c>
       <c r="C1145" s="2" t="n">
-        <v>627.1</v>
+        <v>641.25</v>
       </c>
       <c r="D1145" s="2" t="n">
         <v>602</v>
@@ -18821,7 +18821,7 @@
         <v>1691.8</v>
       </c>
       <c r="C1149" s="2" t="n">
-        <v>1574.6</v>
+        <v>1589.3</v>
       </c>
       <c r="D1149" s="2" t="n">
         <v>1423.1</v>
@@ -18888,7 +18888,7 @@
         <v>81.04000000000001</v>
       </c>
       <c r="D1153" s="2" t="n">
-        <v>80.62</v>
+        <v>81.04000000000001</v>
       </c>
     </row>
     <row r="1154">
@@ -19333,7 +19333,7 @@
         <v>299.3</v>
       </c>
       <c r="C1181" s="2" t="n">
-        <v>289.2</v>
+        <v>291</v>
       </c>
       <c r="D1181" s="2" t="n">
         <v>289.2</v>
@@ -19381,7 +19381,7 @@
         <v>841.55</v>
       </c>
       <c r="C1184" s="2" t="n">
-        <v>801.35</v>
+        <v>807.8</v>
       </c>
       <c r="D1184" s="2" t="n">
         <v>786.85</v>
@@ -19429,7 +19429,7 @@
         <v>628</v>
       </c>
       <c r="C1187" s="2" t="n">
-        <v>622.35</v>
+        <v>626.45</v>
       </c>
       <c r="D1187" s="2" t="n">
         <v>620.15</v>
@@ -19573,7 +19573,7 @@
         <v>654.5</v>
       </c>
       <c r="C1196" s="2" t="n">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="D1196" s="2" t="n">
         <v>555</v>
@@ -19608,7 +19608,7 @@
         <v>86.40000000000001</v>
       </c>
       <c r="D1198" s="2" t="n">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="1199">
@@ -19829,10 +19829,10 @@
         <v>5.76</v>
       </c>
       <c r="C1212" s="2" t="n">
-        <v>5.16</v>
+        <v>5.18</v>
       </c>
       <c r="D1212" s="2" t="n">
-        <v>4.82</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="1213">
@@ -19893,7 +19893,7 @@
         <v>1062.1</v>
       </c>
       <c r="C1216" s="2" t="n">
-        <v>990.1</v>
+        <v>992.9</v>
       </c>
       <c r="D1216" s="2" t="n">
         <v>980.4</v>
@@ -20456,7 +20456,7 @@
         <v>44.03</v>
       </c>
       <c r="D1251" s="2" t="n">
-        <v>42.99</v>
+        <v>43.11</v>
       </c>
     </row>
     <row r="1252">
@@ -20501,7 +20501,7 @@
         <v>31.47</v>
       </c>
       <c r="C1254" s="2" t="n">
-        <v>29.42</v>
+        <v>29.44</v>
       </c>
       <c r="D1254" s="2" t="n">
         <v>29.18</v>
@@ -20661,7 +20661,7 @@
         <v>368</v>
       </c>
       <c r="C1264" s="2" t="n">
-        <v>346.25</v>
+        <v>350.1</v>
       </c>
       <c r="D1264" s="2" t="n">
         <v>340</v>
@@ -20933,7 +20933,7 @@
         <v>31.1</v>
       </c>
       <c r="C1281" s="2" t="n">
-        <v>27.26</v>
+        <v>28</v>
       </c>
       <c r="D1281" s="2" t="n">
         <v>23.91</v>
@@ -21176,7 +21176,7 @@
         <v>8.640000000000001</v>
       </c>
       <c r="D1296" s="2" t="n">
-        <v>7.91</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="1297">
@@ -21381,10 +21381,10 @@
         <v>108</v>
       </c>
       <c r="C1309" s="2" t="n">
-        <v>95.05</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="D1309" s="2" t="n">
-        <v>89.42</v>
+        <v>92.34999999999999</v>
       </c>
     </row>
     <row r="1310">
@@ -21877,7 +21877,7 @@
         <v>187.15</v>
       </c>
       <c r="C1340" s="2" t="n">
-        <v>182.59</v>
+        <v>183.7</v>
       </c>
       <c r="D1340" s="2" t="n">
         <v>180</v>
@@ -21957,7 +21957,7 @@
         <v>1220.6</v>
       </c>
       <c r="C1345" s="2" t="n">
-        <v>1201.2</v>
+        <v>1204</v>
       </c>
       <c r="D1345" s="2" t="n">
         <v>1167</v>
@@ -22037,7 +22037,7 @@
         <v>571</v>
       </c>
       <c r="C1350" s="2" t="n">
-        <v>542.55</v>
+        <v>550.05</v>
       </c>
       <c r="D1350" s="2" t="n">
         <v>522.5</v>
@@ -22261,7 +22261,7 @@
         <v>349.6</v>
       </c>
       <c r="C1364" s="2" t="n">
-        <v>320.7</v>
+        <v>328</v>
       </c>
       <c r="D1364" s="2" t="n">
         <v>311.4</v>
@@ -22453,7 +22453,7 @@
         <v>4640.6</v>
       </c>
       <c r="C1376" s="2" t="n">
-        <v>4495</v>
+        <v>4502.2</v>
       </c>
       <c r="D1376" s="2" t="n">
         <v>4424.2</v>
@@ -22648,7 +22648,7 @@
         <v>223.2</v>
       </c>
       <c r="D1388" s="2" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1389">
@@ -22709,7 +22709,7 @@
         <v>203.29</v>
       </c>
       <c r="C1392" s="2" t="n">
-        <v>169.96</v>
+        <v>181.3</v>
       </c>
       <c r="D1392" s="2" t="n">
         <v>169.82</v>
@@ -22824,7 +22824,7 @@
         <v>366.05</v>
       </c>
       <c r="D1399" s="2" t="n">
-        <v>324.5</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1400">
@@ -23048,7 +23048,7 @@
         <v>246</v>
       </c>
       <c r="D1413" s="2" t="n">
-        <v>226.2</v>
+        <v>233.15</v>
       </c>
     </row>
     <row r="1414">
@@ -23061,7 +23061,7 @@
         <v>439</v>
       </c>
       <c r="C1414" s="2" t="n">
-        <v>429</v>
+        <v>432.95</v>
       </c>
       <c r="D1414" s="2" t="n">
         <v>394.7</v>
@@ -23125,7 +23125,7 @@
         <v>148</v>
       </c>
       <c r="C1418" s="2" t="n">
-        <v>142</v>
+        <v>142.51</v>
       </c>
       <c r="D1418" s="2" t="n">
         <v>123.12</v>
@@ -23141,7 +23141,7 @@
         <v>33.7</v>
       </c>
       <c r="C1419" s="2" t="n">
-        <v>29.22</v>
+        <v>30.45</v>
       </c>
       <c r="D1419" s="2" t="n">
         <v>24.55</v>
@@ -24021,7 +24021,7 @@
         <v>197</v>
       </c>
       <c r="C1474" s="2" t="n">
-        <v>190</v>
+        <v>190.31</v>
       </c>
       <c r="D1474" s="2" t="n">
         <v>188.21</v>
@@ -24056,7 +24056,7 @@
         <v>3.3</v>
       </c>
       <c r="D1476" s="2" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="1477">
@@ -24197,7 +24197,7 @@
         <v>1677.4</v>
       </c>
       <c r="C1485" s="2" t="n">
-        <v>1644.1</v>
+        <v>1646</v>
       </c>
       <c r="D1485" s="2" t="n">
         <v>1640</v>
@@ -24248,7 +24248,7 @@
         <v>10.79</v>
       </c>
       <c r="D1488" s="2" t="n">
-        <v>10.19</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="1489">
@@ -24277,7 +24277,7 @@
         <v>564</v>
       </c>
       <c r="C1490" s="2" t="n">
-        <v>497.2</v>
+        <v>519.4</v>
       </c>
       <c r="D1490" s="2" t="n">
         <v>497.2</v>
@@ -24472,7 +24472,7 @@
         <v>1056.25</v>
       </c>
       <c r="D1502" s="2" t="n">
-        <v>1051.75</v>
+        <v>1051.89</v>
       </c>
     </row>
     <row r="1503">
@@ -24501,7 +24501,7 @@
         <v>1126.72</v>
       </c>
       <c r="C1504" s="2" t="n">
-        <v>1115.35</v>
+        <v>1124.27</v>
       </c>
       <c r="D1504" s="2" t="n">
         <v>1115.35</v>
@@ -24517,10 +24517,10 @@
         <v>1148.98</v>
       </c>
       <c r="C1505" s="2" t="n">
-        <v>1148.01</v>
+        <v>1148.18</v>
       </c>
       <c r="D1505" s="2" t="n">
-        <v>1144.55</v>
+        <v>1144.73</v>
       </c>
     </row>
     <row r="1506">
@@ -24533,7 +24533,7 @@
         <v>999.99</v>
       </c>
       <c r="C1506" s="2" t="n">
-        <v>999.3</v>
+        <v>999.36</v>
       </c>
       <c r="D1506" s="2" t="n">
         <v>994.99</v>
@@ -24549,7 +24549,7 @@
         <v>1011.83</v>
       </c>
       <c r="C1507" s="2" t="n">
-        <v>1010.57</v>
+        <v>1010.85</v>
       </c>
       <c r="D1507" s="2" t="n">
         <v>981.86</v>
@@ -24581,10 +24581,10 @@
         <v>116.36</v>
       </c>
       <c r="C1509" s="2" t="n">
-        <v>116.25</v>
+        <v>116.26</v>
       </c>
       <c r="D1509" s="2" t="n">
-        <v>115.9</v>
+        <v>115.91</v>
       </c>
     </row>
     <row r="1510">
@@ -24661,10 +24661,10 @@
         <v>1125.44</v>
       </c>
       <c r="C1514" s="2" t="n">
-        <v>1124.54</v>
+        <v>1124.7</v>
       </c>
       <c r="D1514" s="2" t="n">
-        <v>1121.3</v>
+        <v>1121.44</v>
       </c>
     </row>
     <row r="1515">
@@ -24677,7 +24677,7 @@
         <v>14.42</v>
       </c>
       <c r="C1515" s="2" t="n">
-        <v>13.01</v>
+        <v>13.25</v>
       </c>
       <c r="D1515" s="2" t="n">
         <v>13.01</v>
@@ -25045,7 +25045,7 @@
         <v>4215</v>
       </c>
       <c r="C1538" s="2" t="n">
-        <v>3905.6</v>
+        <v>3915</v>
       </c>
       <c r="D1538" s="2" t="n">
         <v>3905.6</v>
@@ -25336,7 +25336,7 @@
         <v>265.51</v>
       </c>
       <c r="D1556" s="2" t="n">
-        <v>221</v>
+        <v>226.55</v>
       </c>
     </row>
     <row r="1557">
@@ -25397,7 +25397,7 @@
         <v>83.73999999999999</v>
       </c>
       <c r="C1560" s="2" t="n">
-        <v>79.89</v>
+        <v>81.88</v>
       </c>
       <c r="D1560" s="2" t="n">
         <v>78.87</v>
@@ -25637,7 +25637,7 @@
         <v>31.31</v>
       </c>
       <c r="C1575" s="2" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="D1575" s="2" t="n">
         <v>30.2</v>
@@ -25765,7 +25765,7 @@
         <v>140.99</v>
       </c>
       <c r="C1583" s="2" t="n">
-        <v>139.2</v>
+        <v>139.49</v>
       </c>
       <c r="D1583" s="2" t="n">
         <v>125.55</v>
@@ -25880,7 +25880,7 @@
         <v>2342</v>
       </c>
       <c r="D1590" s="2" t="n">
-        <v>2222</v>
+        <v>2242.1</v>
       </c>
     </row>
     <row r="1591">
@@ -26101,7 +26101,7 @@
         <v>131.4</v>
       </c>
       <c r="C1604" s="2" t="n">
-        <v>122.38</v>
+        <v>124.32</v>
       </c>
       <c r="D1604" s="2" t="n">
         <v>113.4</v>
@@ -26168,7 +26168,7 @@
         <v>108</v>
       </c>
       <c r="D1608" s="2" t="n">
-        <v>91.36</v>
+        <v>93.01000000000001</v>
       </c>
     </row>
     <row r="1609">
@@ -26181,7 +26181,7 @@
         <v>1711.6</v>
       </c>
       <c r="C1609" s="2" t="n">
-        <v>1598.1</v>
+        <v>1612.1</v>
       </c>
       <c r="D1609" s="2" t="n">
         <v>1514.6</v>
@@ -26213,7 +26213,7 @@
         <v>537</v>
       </c>
       <c r="C1611" s="2" t="n">
-        <v>507.85</v>
+        <v>510</v>
       </c>
       <c r="D1611" s="2" t="n">
         <v>485.6</v>
@@ -26373,7 +26373,7 @@
         <v>273.99</v>
       </c>
       <c r="C1621" s="2" t="n">
-        <v>250.26</v>
+        <v>261.6</v>
       </c>
       <c r="D1621" s="2" t="n">
         <v>245.8</v>
@@ -26485,7 +26485,7 @@
         <v>1280</v>
       </c>
       <c r="C1628" s="2" t="n">
-        <v>1258.8</v>
+        <v>1270.9</v>
       </c>
       <c r="D1628" s="2" t="n">
         <v>1258.8</v>
@@ -26520,7 +26520,7 @@
         <v>290.05</v>
       </c>
       <c r="D1630" s="2" t="n">
-        <v>289.45</v>
+        <v>290.05</v>
       </c>
     </row>
     <row r="1631">
@@ -26741,7 +26741,7 @@
         <v>960</v>
       </c>
       <c r="C1644" s="2" t="n">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="D1644" s="2" t="n">
         <v>807</v>
@@ -27285,10 +27285,10 @@
         <v>3.93</v>
       </c>
       <c r="C1678" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="D1678" s="2" t="n">
         <v>3.77</v>
-      </c>
-      <c r="D1678" s="2" t="n">
-        <v>3.68</v>
       </c>
     </row>
     <row r="1679">
@@ -27301,7 +27301,7 @@
         <v>87</v>
       </c>
       <c r="C1679" s="2" t="n">
-        <v>84</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D1679" s="2" t="n">
         <v>71.02</v>
@@ -27333,7 +27333,7 @@
         <v>485</v>
       </c>
       <c r="C1681" s="2" t="n">
-        <v>470.6</v>
+        <v>475.15</v>
       </c>
       <c r="D1681" s="2" t="n">
         <v>430.75</v>
@@ -27589,7 +27589,7 @@
         <v>64.84999999999999</v>
       </c>
       <c r="C1697" s="2" t="n">
-        <v>60.83</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D1697" s="2" t="n">
         <v>60.83</v>
@@ -28056,7 +28056,7 @@
         <v>50</v>
       </c>
       <c r="D1726" s="2" t="n">
-        <v>36</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="1727">
@@ -28069,7 +28069,7 @@
         <v>23.78</v>
       </c>
       <c r="C1727" s="2" t="n">
-        <v>23.31</v>
+        <v>23.4</v>
       </c>
       <c r="D1727" s="2" t="n">
         <v>23.31</v>
@@ -28101,7 +28101,7 @@
         <v>250.5</v>
       </c>
       <c r="C1729" s="2" t="n">
-        <v>219.5</v>
+        <v>221.05</v>
       </c>
       <c r="D1729" s="2" t="n">
         <v>164.01</v>
@@ -28325,7 +28325,7 @@
         <v>25.68</v>
       </c>
       <c r="C1743" s="2" t="n">
-        <v>25.06</v>
+        <v>25.18</v>
       </c>
       <c r="D1743" s="2" t="n">
         <v>24.26</v>
@@ -28389,7 +28389,7 @@
         <v>2466.3</v>
       </c>
       <c r="C1747" s="2" t="n">
-        <v>2274.6</v>
+        <v>2280.8</v>
       </c>
       <c r="D1747" s="2" t="n">
         <v>2144.8</v>
@@ -28581,7 +28581,7 @@
         <v>1.7</v>
       </c>
       <c r="C1759" s="2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="D1759" s="2" t="n">
         <v>1.58</v>
@@ -28837,7 +28837,7 @@
         <v>213.7</v>
       </c>
       <c r="C1775" s="2" t="n">
-        <v>201.31</v>
+        <v>203.85</v>
       </c>
       <c r="D1775" s="2" t="n">
         <v>185.15</v>
@@ -28856,7 +28856,7 @@
         <v>39.79</v>
       </c>
       <c r="D1776" s="2" t="n">
-        <v>38.25</v>
+        <v>38.52</v>
       </c>
     </row>
     <row r="1777">
@@ -28920,7 +28920,7 @@
         <v>26.3</v>
       </c>
       <c r="D1780" s="2" t="n">
-        <v>22.31</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="1781">
@@ -29333,7 +29333,7 @@
         <v>118</v>
       </c>
       <c r="C1806" s="2" t="n">
-        <v>116.35</v>
+        <v>117</v>
       </c>
       <c r="D1806" s="2" t="n">
         <v>115.89</v>
@@ -29429,7 +29429,7 @@
         <v>136.95</v>
       </c>
       <c r="C1812" s="2" t="n">
-        <v>125.72</v>
+        <v>132.31</v>
       </c>
       <c r="D1812" s="2" t="n">
         <v>102.32</v>
@@ -29765,7 +29765,7 @@
         <v>36.46</v>
       </c>
       <c r="C1833" s="2" t="n">
-        <v>36</v>
+        <v>36.46</v>
       </c>
       <c r="D1833" s="2" t="n">
         <v>31.57</v>
@@ -30296,7 +30296,7 @@
         <v>176.61</v>
       </c>
       <c r="D1866" s="2" t="n">
-        <v>163.5</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1867">
@@ -30344,7 +30344,7 @@
         <v>26.51</v>
       </c>
       <c r="D1869" s="2" t="n">
-        <v>25.7</v>
+        <v>26.51</v>
       </c>
     </row>
     <row r="1870">
@@ -30440,7 +30440,7 @@
         <v>1610.1</v>
       </c>
       <c r="D1875" s="2" t="n">
-        <v>1584</v>
+        <v>1602.2</v>
       </c>
     </row>
     <row r="1876">
@@ -30453,7 +30453,7 @@
         <v>77.88</v>
       </c>
       <c r="C1876" s="2" t="n">
-        <v>75.3</v>
+        <v>75.8</v>
       </c>
       <c r="D1876" s="2" t="n">
         <v>71.98</v>
@@ -30469,7 +30469,7 @@
         <v>60.99</v>
       </c>
       <c r="C1877" s="2" t="n">
-        <v>51.3</v>
+        <v>57</v>
       </c>
       <c r="D1877" s="2" t="n">
         <v>50</v>
@@ -30533,7 +30533,7 @@
         <v>3.83</v>
       </c>
       <c r="C1881" s="2" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="D1881" s="2" t="n">
         <v>3.47</v>
@@ -30648,7 +30648,7 @@
         <v>625.35</v>
       </c>
       <c r="D1888" s="2" t="n">
-        <v>561.65</v>
+        <v>601.5</v>
       </c>
     </row>
     <row r="1889">
@@ -30984,7 +30984,7 @@
         <v>6.28</v>
       </c>
       <c r="D1909" s="2" t="n">
-        <v>6.11</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="1910">
@@ -31032,7 +31032,7 @@
         <v>82.84</v>
       </c>
       <c r="D1912" s="2" t="n">
-        <v>59.3</v>
+        <v>61.01</v>
       </c>
     </row>
     <row r="1913">
@@ -31173,7 +31173,7 @@
         <v>163.43</v>
       </c>
       <c r="C1921" s="2" t="n">
-        <v>157</v>
+        <v>159.41</v>
       </c>
       <c r="D1921" s="2" t="n">
         <v>150.2</v>
@@ -31205,10 +31205,10 @@
         <v>50.7</v>
       </c>
       <c r="C1923" s="2" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="D1923" s="2" t="n">
-        <v>30.65</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="1924">
@@ -31285,7 +31285,7 @@
         <v>377</v>
       </c>
       <c r="C1928" s="2" t="n">
-        <v>339</v>
+        <v>352.65</v>
       </c>
       <c r="D1928" s="2" t="n">
         <v>291.2</v>
@@ -31301,10 +31301,10 @@
         <v>55.1</v>
       </c>
       <c r="C1929" s="2" t="n">
-        <v>48.55</v>
+        <v>49.5</v>
       </c>
       <c r="D1929" s="2" t="n">
-        <v>46.28</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="1930">
@@ -31317,7 +31317,7 @@
         <v>325.2</v>
       </c>
       <c r="C1930" s="2" t="n">
-        <v>291.95</v>
+        <v>293.35</v>
       </c>
       <c r="D1930" s="2" t="n">
         <v>274.8</v>
@@ -31336,7 +31336,7 @@
         <v>730.65</v>
       </c>
       <c r="D1931" s="2" t="n">
-        <v>540</v>
+        <v>567.85</v>
       </c>
     </row>
     <row r="1932">
@@ -31493,7 +31493,7 @@
         <v>172.35</v>
       </c>
       <c r="C1941" s="2" t="n">
-        <v>158.76</v>
+        <v>160.6</v>
       </c>
       <c r="D1941" s="2" t="n">
         <v>151.65</v>
@@ -31605,7 +31605,7 @@
         <v>544.05</v>
       </c>
       <c r="C1948" s="2" t="n">
-        <v>539</v>
+        <v>540.75</v>
       </c>
       <c r="D1948" s="2" t="n">
         <v>530.05</v>
@@ -31781,7 +31781,7 @@
         <v>71.16</v>
       </c>
       <c r="C1959" s="2" t="n">
-        <v>68.66</v>
+        <v>69.91</v>
       </c>
       <c r="D1959" s="2" t="n">
         <v>68.66</v>
@@ -31893,7 +31893,7 @@
         <v>271.9</v>
       </c>
       <c r="C1966" s="2" t="n">
-        <v>251.1</v>
+        <v>255</v>
       </c>
       <c r="D1966" s="2" t="n">
         <v>250.6</v>
@@ -32053,7 +32053,7 @@
         <v>2.41</v>
       </c>
       <c r="C1976" s="2" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="D1976" s="2" t="n">
         <v>1.72</v>
@@ -32088,7 +32088,7 @@
         <v>66.76000000000001</v>
       </c>
       <c r="D1978" s="2" t="n">
-        <v>66.06</v>
+        <v>66.18000000000001</v>
       </c>
     </row>
     <row r="1979">
@@ -32133,7 +32133,7 @@
         <v>243</v>
       </c>
       <c r="C1981" s="2" t="n">
-        <v>223</v>
+        <v>223.01</v>
       </c>
       <c r="D1981" s="2" t="n">
         <v>201.25</v>
@@ -32245,7 +32245,7 @@
         <v>14.07</v>
       </c>
       <c r="C1988" s="2" t="n">
-        <v>12.87</v>
+        <v>13.42</v>
       </c>
       <c r="D1988" s="2" t="n">
         <v>11.81</v>
@@ -32389,7 +32389,7 @@
         <v>342.05</v>
       </c>
       <c r="C1997" s="2" t="n">
-        <v>321.95</v>
+        <v>322.85</v>
       </c>
       <c r="D1997" s="2" t="n">
         <v>313.35</v>
@@ -32744,7 +32744,7 @@
         <v>1728</v>
       </c>
       <c r="D2019" s="2" t="n">
-        <v>1709.9</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="2020">
@@ -32837,7 +32837,7 @@
         <v>116.55</v>
       </c>
       <c r="C2025" s="2" t="n">
-        <v>110.55</v>
+        <v>113.71</v>
       </c>
       <c r="D2025" s="2" t="n">
         <v>109.37</v>
@@ -32869,7 +32869,7 @@
         <v>1224.8</v>
       </c>
       <c r="C2027" s="2" t="n">
-        <v>1105.1</v>
+        <v>1131.2</v>
       </c>
       <c r="D2027" s="2" t="n">
         <v>1065.4</v>
@@ -32933,7 +32933,7 @@
         <v>678</v>
       </c>
       <c r="C2031" s="2" t="n">
-        <v>549.9</v>
+        <v>625</v>
       </c>
       <c r="D2031" s="2" t="n">
         <v>481.7</v>
@@ -33253,7 +33253,7 @@
         <v>689</v>
       </c>
       <c r="C2051" s="2" t="n">
-        <v>572.2</v>
+        <v>579.95</v>
       </c>
       <c r="D2051" s="2" t="n">
         <v>440</v>
@@ -33269,7 +33269,7 @@
         <v>18.5</v>
       </c>
       <c r="C2052" s="2" t="n">
-        <v>17.67</v>
+        <v>17.75</v>
       </c>
       <c r="D2052" s="2" t="n">
         <v>17.25</v>
@@ -33429,7 +33429,7 @@
         <v>689</v>
       </c>
       <c r="C2062" s="2" t="n">
-        <v>682.1</v>
+        <v>685</v>
       </c>
       <c r="D2062" s="2" t="n">
         <v>663.1</v>
@@ -33528,7 +33528,7 @@
         <v>280</v>
       </c>
       <c r="D2068" s="2" t="n">
-        <v>274</v>
+        <v>275.05</v>
       </c>
     </row>
     <row r="2069">
@@ -33781,7 +33781,7 @@
         <v>82.5</v>
       </c>
       <c r="C2084" s="2" t="n">
-        <v>79.31999999999999</v>
+        <v>80</v>
       </c>
       <c r="D2084" s="2" t="n">
         <v>78.79000000000001</v>
@@ -33797,7 +33797,7 @@
         <v>81.69</v>
       </c>
       <c r="C2085" s="2" t="n">
-        <v>79.03</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="D2085" s="2" t="n">
         <v>79.03</v>
@@ -33861,7 +33861,7 @@
         <v>25385</v>
       </c>
       <c r="C2089" s="2" t="n">
-        <v>23755</v>
+        <v>24105</v>
       </c>
       <c r="D2089" s="2" t="n">
         <v>21510</v>
@@ -33941,7 +33941,7 @@
         <v>1408.4</v>
       </c>
       <c r="C2094" s="2" t="n">
-        <v>1276</v>
+        <v>1301</v>
       </c>
       <c r="D2094" s="2" t="n">
         <v>1181.2</v>
@@ -34037,7 +34037,7 @@
         <v>139.05</v>
       </c>
       <c r="C2100" s="2" t="n">
-        <v>130.7</v>
+        <v>135.05</v>
       </c>
       <c r="D2100" s="2" t="n">
         <v>117.71</v>
@@ -34088,7 +34088,7 @@
         <v>177.1</v>
       </c>
       <c r="D2103" s="2" t="n">
-        <v>150.4</v>
+        <v>157.98</v>
       </c>
     </row>
     <row r="2104">
@@ -34136,7 +34136,7 @@
         <v>458.1</v>
       </c>
       <c r="D2106" s="2" t="n">
-        <v>428.2</v>
+        <v>458.1</v>
       </c>
     </row>
     <row r="2107">
@@ -34216,7 +34216,7 @@
         <v>51</v>
       </c>
       <c r="D2111" s="2" t="n">
-        <v>38.49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2112">
@@ -34277,7 +34277,7 @@
         <v>67</v>
       </c>
       <c r="C2115" s="2" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D2115" s="2" t="n">
         <v>65.55</v>
@@ -34357,7 +34357,7 @@
         <v>220.4</v>
       </c>
       <c r="C2120" s="2" t="n">
-        <v>210.26</v>
+        <v>210.45</v>
       </c>
       <c r="D2120" s="2" t="n">
         <v>191.04</v>
@@ -34373,7 +34373,7 @@
         <v>1220.5</v>
       </c>
       <c r="C2121" s="2" t="n">
-        <v>1198</v>
+        <v>1210</v>
       </c>
       <c r="D2121" s="2" t="n">
         <v>1198</v>
@@ -34421,7 +34421,7 @@
         <v>60.58</v>
       </c>
       <c r="C2124" s="2" t="n">
-        <v>56.76</v>
+        <v>57.5</v>
       </c>
       <c r="D2124" s="2" t="n">
         <v>51</v>
@@ -34469,7 +34469,7 @@
         <v>22.07</v>
       </c>
       <c r="C2127" s="2" t="n">
-        <v>20.41</v>
+        <v>20.81</v>
       </c>
       <c r="D2127" s="2" t="n">
         <v>19.6</v>
@@ -34504,7 +34504,7 @@
         <v>9.51</v>
       </c>
       <c r="D2129" s="2" t="n">
-        <v>7.7</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="2130">
@@ -34581,7 +34581,7 @@
         <v>373.9</v>
       </c>
       <c r="C2134" s="2" t="n">
-        <v>327.25</v>
+        <v>346</v>
       </c>
       <c r="D2134" s="2" t="n">
         <v>242.01</v>
@@ -34760,7 +34760,7 @@
         <v>1115</v>
       </c>
       <c r="D2145" s="2" t="n">
-        <v>835.05</v>
+        <v>937.3</v>
       </c>
     </row>
     <row r="2146">
@@ -35000,7 +35000,7 @@
         <v>110.37</v>
       </c>
       <c r="D2160" s="2" t="n">
-        <v>108.6</v>
+        <v>110.37</v>
       </c>
     </row>
     <row r="2161">
@@ -35061,7 +35061,7 @@
         <v>56.95</v>
       </c>
       <c r="C2164" s="2" t="n">
-        <v>53.8</v>
+        <v>54.65</v>
       </c>
       <c r="D2164" s="2" t="n">
         <v>42.56</v>
@@ -35141,7 +35141,7 @@
         <v>57.15</v>
       </c>
       <c r="C2169" s="2" t="n">
-        <v>54.05</v>
+        <v>54.58</v>
       </c>
       <c r="D2169" s="2" t="n">
         <v>54.05</v>
@@ -35157,7 +35157,7 @@
         <v>313.15</v>
       </c>
       <c r="C2170" s="2" t="n">
-        <v>287</v>
+        <v>289.95</v>
       </c>
       <c r="D2170" s="2" t="n">
         <v>276.1</v>
@@ -35528,7 +35528,7 @@
         <v>4.9</v>
       </c>
       <c r="D2193" s="2" t="n">
-        <v>4.42</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="2194">
@@ -35573,7 +35573,7 @@
         <v>52</v>
       </c>
       <c r="C2196" s="2" t="n">
-        <v>49.82</v>
+        <v>50.6</v>
       </c>
       <c r="D2196" s="2" t="n">
         <v>48.98</v>
@@ -35592,7 +35592,7 @@
         <v>1477</v>
       </c>
       <c r="D2197" s="2" t="n">
-        <v>1189.2</v>
+        <v>1211.8</v>
       </c>
     </row>
     <row r="2198">
@@ -36005,7 +36005,7 @@
         <v>18.76</v>
       </c>
       <c r="C2223" s="2" t="n">
-        <v>17.61</v>
+        <v>18.54</v>
       </c>
       <c r="D2223" s="2" t="n">
         <v>17.61</v>
@@ -36056,7 +36056,7 @@
         <v>344.95</v>
       </c>
       <c r="D2226" s="2" t="n">
-        <v>331.9</v>
+        <v>333.55</v>
       </c>
     </row>
     <row r="2227">
@@ -36341,7 +36341,7 @@
         <v>153</v>
       </c>
       <c r="C2244" s="2" t="n">
-        <v>140</v>
+        <v>142.13</v>
       </c>
       <c r="D2244" s="2" t="n">
         <v>136</v>
@@ -36549,7 +36549,7 @@
         <v>5.77</v>
       </c>
       <c r="C2257" s="2" t="n">
-        <v>4.99</v>
+        <v>5.02</v>
       </c>
       <c r="D2257" s="2" t="n">
         <v>4.99</v>
@@ -37029,7 +37029,7 @@
         <v>64.98999999999999</v>
       </c>
       <c r="C2287" s="2" t="n">
-        <v>61.05</v>
+        <v>61.55</v>
       </c>
       <c r="D2287" s="2" t="n">
         <v>45.75</v>
@@ -37093,7 +37093,7 @@
         <v>47.03</v>
       </c>
       <c r="C2291" s="2" t="n">
-        <v>46.1</v>
+        <v>46.54</v>
       </c>
       <c r="D2291" s="2" t="n">
         <v>45.77</v>
@@ -37221,10 +37221,10 @@
         <v>1059.91</v>
       </c>
       <c r="C2299" s="2" t="n">
-        <v>1059.04</v>
+        <v>1059.18</v>
       </c>
       <c r="D2299" s="2" t="n">
-        <v>1055.8</v>
+        <v>1055.93</v>
       </c>
     </row>
     <row r="2300">
@@ -37349,7 +37349,7 @@
         <v>51</v>
       </c>
       <c r="C2307" s="2" t="n">
-        <v>46.75</v>
+        <v>48.5</v>
       </c>
       <c r="D2307" s="2" t="n">
         <v>45.31</v>
@@ -37525,7 +37525,7 @@
         <v>152.8</v>
       </c>
       <c r="C2318" s="2" t="n">
-        <v>130.41</v>
+        <v>137.4</v>
       </c>
       <c r="D2318" s="2" t="n">
         <v>128.8</v>
@@ -37560,7 +37560,7 @@
         <v>3104.6</v>
       </c>
       <c r="D2320" s="2" t="n">
-        <v>2878.1</v>
+        <v>2896.9</v>
       </c>
     </row>
     <row r="2321">
@@ -37669,7 +37669,7 @@
         <v>336.8</v>
       </c>
       <c r="C2327" s="2" t="n">
-        <v>315</v>
+        <v>323.85</v>
       </c>
       <c r="D2327" s="2" t="n">
         <v>310.15</v>
@@ -37960,7 +37960,7 @@
         <v>12.36</v>
       </c>
       <c r="D2345" s="2" t="n">
-        <v>12.2</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="2346">
@@ -38021,7 +38021,7 @@
         <v>9.720000000000001</v>
       </c>
       <c r="C2349" s="2" t="n">
-        <v>8.609999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="D2349" s="2" t="n">
         <v>8.42</v>
@@ -38088,7 +38088,7 @@
         <v>657.05</v>
       </c>
       <c r="D2353" s="2" t="n">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2354">
@@ -38245,7 +38245,7 @@
         <v>5.5</v>
       </c>
       <c r="C2363" s="2" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="D2363" s="2" t="n">
         <v>5.07</v>
@@ -38392,7 +38392,7 @@
         <v>21.05</v>
       </c>
       <c r="D2372" s="2" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2373">
@@ -38613,10 +38613,10 @@
         <v>551.3</v>
       </c>
       <c r="C2386" s="2" t="n">
-        <v>540</v>
+        <v>550.2</v>
       </c>
       <c r="D2386" s="2" t="n">
-        <v>462.05</v>
+        <v>463.5</v>
       </c>
     </row>
     <row r="2387">
@@ -38648,7 +38648,7 @@
         <v>370.6</v>
       </c>
       <c r="D2388" s="2" t="n">
-        <v>368.25</v>
+        <v>370.6</v>
       </c>
     </row>
     <row r="2389">
@@ -38789,7 +38789,7 @@
         <v>129</v>
       </c>
       <c r="C2397" s="2" t="n">
-        <v>127.1</v>
+        <v>128.8</v>
       </c>
       <c r="D2397" s="2" t="n">
         <v>122</v>
@@ -38933,7 +38933,7 @@
         <v>1099</v>
       </c>
       <c r="C2406" s="2" t="n">
-        <v>1043.7</v>
+        <v>1048.1</v>
       </c>
       <c r="D2406" s="2" t="n">
         <v>1015</v>
@@ -39461,7 +39461,7 @@
         <v>144.8</v>
       </c>
       <c r="C2439" s="2" t="n">
-        <v>114.03</v>
+        <v>125.4</v>
       </c>
       <c r="D2439" s="2" t="n">
         <v>113.75</v>
@@ -39877,7 +39877,7 @@
         <v>75.40000000000001</v>
       </c>
       <c r="C2465" s="2" t="n">
-        <v>70.16</v>
+        <v>73.94</v>
       </c>
       <c r="D2465" s="2" t="n">
         <v>57.8</v>
@@ -39909,7 +39909,7 @@
         <v>34.65</v>
       </c>
       <c r="C2467" s="2" t="n">
-        <v>33.75</v>
+        <v>33.77</v>
       </c>
       <c r="D2467" s="2" t="n">
         <v>33.51</v>
@@ -40181,7 +40181,7 @@
         <v>49.22</v>
       </c>
       <c r="C2484" s="2" t="n">
-        <v>46.11</v>
+        <v>46.15</v>
       </c>
       <c r="D2484" s="2" t="n">
         <v>44.54</v>
@@ -40296,7 +40296,7 @@
         <v>3450</v>
       </c>
       <c r="D2491" s="2" t="n">
-        <v>2752</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="2492">
@@ -40453,7 +40453,7 @@
         <v>2492</v>
       </c>
       <c r="C2501" s="2" t="n">
-        <v>2434.9</v>
+        <v>2435.1</v>
       </c>
       <c r="D2501" s="2" t="n">
         <v>2417.9</v>
@@ -40808,7 +40808,7 @@
         <v>20.9</v>
       </c>
       <c r="D2523" s="2" t="n">
-        <v>18.7</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="2524">
@@ -40853,7 +40853,7 @@
         <v>419</v>
       </c>
       <c r="C2526" s="2" t="n">
-        <v>400.1</v>
+        <v>410</v>
       </c>
       <c r="D2526" s="2" t="n">
         <v>389.15</v>
@@ -41048,7 +41048,7 @@
         <v>40</v>
       </c>
       <c r="D2538" s="2" t="n">
-        <v>39.56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2539">
@@ -41781,7 +41781,7 @@
         <v>2955</v>
       </c>
       <c r="C2584" s="2" t="n">
-        <v>2660</v>
+        <v>2670</v>
       </c>
       <c r="D2584" s="2" t="n">
         <v>2520.2</v>
@@ -41989,7 +41989,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="C2597" s="2" t="n">
-        <v>71.59</v>
+        <v>73</v>
       </c>
       <c r="D2597" s="2" t="n">
         <v>69.58</v>
@@ -42053,7 +42053,7 @@
         <v>12.06</v>
       </c>
       <c r="C2601" s="2" t="n">
-        <v>11.54</v>
+        <v>12.06</v>
       </c>
       <c r="D2601" s="2" t="n">
         <v>11.51</v>
@@ -42101,10 +42101,10 @@
         <v>326</v>
       </c>
       <c r="C2604" s="2" t="n">
-        <v>308</v>
+        <v>315.55</v>
       </c>
       <c r="D2604" s="2" t="n">
-        <v>238</v>
+        <v>259.55</v>
       </c>
     </row>
     <row r="2605">
@@ -42117,7 +42117,7 @@
         <v>535.75</v>
       </c>
       <c r="C2605" s="2" t="n">
-        <v>488</v>
+        <v>488.25</v>
       </c>
       <c r="D2605" s="2" t="n">
         <v>480.8</v>
@@ -42149,7 +42149,7 @@
         <v>16.41</v>
       </c>
       <c r="C2607" s="2" t="n">
-        <v>11.08</v>
+        <v>12.4</v>
       </c>
       <c r="D2607" s="2" t="n">
         <v>10.8</v>
@@ -42456,7 +42456,7 @@
         <v>540.75</v>
       </c>
       <c r="D2626" s="2" t="n">
-        <v>476.2</v>
+        <v>505.1</v>
       </c>
     </row>
     <row r="2627">
@@ -42677,7 +42677,7 @@
         <v>4204.9</v>
       </c>
       <c r="C2640" s="2" t="n">
-        <v>4080.1</v>
+        <v>4204.9</v>
       </c>
       <c r="D2640" s="2" t="n">
         <v>3575.4</v>
@@ -42757,7 +42757,7 @@
         <v>594</v>
       </c>
       <c r="C2645" s="2" t="n">
-        <v>514.9</v>
+        <v>551</v>
       </c>
       <c r="D2645" s="2" t="n">
         <v>486</v>
@@ -42789,7 +42789,7 @@
         <v>151.21</v>
       </c>
       <c r="C2647" s="2" t="n">
-        <v>100.3</v>
+        <v>110.2</v>
       </c>
       <c r="D2647" s="2" t="n">
         <v>100.3</v>
@@ -42869,7 +42869,7 @@
         <v>157.33</v>
       </c>
       <c r="C2652" s="2" t="n">
-        <v>141.26</v>
+        <v>145</v>
       </c>
       <c r="D2652" s="2" t="n">
         <v>132.93</v>
@@ -42965,7 +42965,7 @@
         <v>4899</v>
       </c>
       <c r="C2658" s="2" t="n">
-        <v>4666</v>
+        <v>4786</v>
       </c>
       <c r="D2658" s="2" t="n">
         <v>4666</v>
@@ -43365,7 +43365,7 @@
         <v>4487</v>
       </c>
       <c r="C2683" s="2" t="n">
-        <v>4335.6</v>
+        <v>4359.5</v>
       </c>
       <c r="D2683" s="2" t="n">
         <v>4335.6</v>
@@ -43653,10 +43653,10 @@
         <v>0.76</v>
       </c>
       <c r="C2701" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="D2701" s="2" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="2702">
@@ -43704,7 +43704,7 @@
         <v>31.71</v>
       </c>
       <c r="D2704" s="2" t="n">
-        <v>28.43</v>
+        <v>30.01</v>
       </c>
     </row>
     <row r="2705">
@@ -43957,7 +43957,7 @@
         <v>4.39</v>
       </c>
       <c r="C2720" s="2" t="n">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
       <c r="D2720" s="2" t="n">
         <v>3.9</v>
@@ -44040,7 +44040,7 @@
         <v>6.8</v>
       </c>
       <c r="D2725" s="2" t="n">
-        <v>6.32</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="2726">
@@ -44197,7 +44197,7 @@
         <v>2.5</v>
       </c>
       <c r="C2735" s="2" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="D2735" s="2" t="n">
         <v>2.39</v>
@@ -44277,7 +44277,7 @@
         <v>233</v>
       </c>
       <c r="C2740" s="2" t="n">
-        <v>160.5</v>
+        <v>161.21</v>
       </c>
       <c r="D2740" s="2" t="n">
         <v>148.87</v>
@@ -44376,7 +44376,7 @@
         <v>52.1</v>
       </c>
       <c r="D2746" s="2" t="n">
-        <v>48.49</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="2747">
@@ -44597,7 +44597,7 @@
         <v>172.22</v>
       </c>
       <c r="C2760" s="2" t="n">
-        <v>165.44</v>
+        <v>169.07</v>
       </c>
       <c r="D2760" s="2" t="n">
         <v>164.81</v>
@@ -44680,7 +44680,7 @@
         <v>44.81</v>
       </c>
       <c r="D2765" s="2" t="n">
-        <v>41</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="2766">
@@ -44853,7 +44853,7 @@
         <v>21.1</v>
       </c>
       <c r="C2776" s="2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="D2776" s="2" t="n">
         <v>17.77</v>
@@ -45013,7 +45013,7 @@
         <v>25.99</v>
       </c>
       <c r="C2786" s="2" t="n">
-        <v>21.81</v>
+        <v>22.11</v>
       </c>
       <c r="D2786" s="2" t="n">
         <v>18.87</v>
@@ -45160,7 +45160,7 @@
         <v>428.3</v>
       </c>
       <c r="D2795" s="2" t="n">
-        <v>358.6</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2796">
@@ -45320,7 +45320,7 @@
         <v>428.95</v>
       </c>
       <c r="D2805" s="2" t="n">
-        <v>403</v>
+        <v>407.15</v>
       </c>
     </row>
     <row r="2806">
@@ -45413,7 +45413,7 @@
         <v>2600.6</v>
       </c>
       <c r="C2811" s="2" t="n">
-        <v>2580</v>
+        <v>2600.6</v>
       </c>
       <c r="D2811" s="2" t="n">
         <v>1765.1</v>
@@ -45493,7 +45493,7 @@
         <v>37.9</v>
       </c>
       <c r="C2816" s="2" t="n">
-        <v>30</v>
+        <v>31.9</v>
       </c>
       <c r="D2816" s="2" t="n">
         <v>26.9</v>
@@ -45544,7 +45544,7 @@
         <v>131.06</v>
       </c>
       <c r="D2819" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2820">
@@ -45557,7 +45557,7 @@
         <v>50</v>
       </c>
       <c r="C2820" s="2" t="n">
-        <v>47.58</v>
+        <v>47.61</v>
       </c>
       <c r="D2820" s="2" t="n">
         <v>45.12</v>
@@ -45576,7 +45576,7 @@
         <v>56.8</v>
       </c>
       <c r="D2821" s="2" t="n">
-        <v>54.62</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="2822">
@@ -45637,7 +45637,7 @@
         <v>148</v>
       </c>
       <c r="C2825" s="2" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D2825" s="2" t="n">
         <v>116</v>
@@ -45957,7 +45957,7 @@
         <v>413</v>
       </c>
       <c r="C2845" s="2" t="n">
-        <v>338.05</v>
+        <v>385</v>
       </c>
       <c r="D2845" s="2" t="n">
         <v>323.95</v>
@@ -45989,7 +45989,7 @@
         <v>0.45</v>
       </c>
       <c r="C2847" s="2" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="D2847" s="2" t="n">
         <v>0.4</v>
@@ -46181,7 +46181,7 @@
         <v>14.05</v>
       </c>
       <c r="C2859" s="2" t="n">
-        <v>12.8</v>
+        <v>13.93</v>
       </c>
       <c r="D2859" s="2" t="n">
         <v>12.8</v>
@@ -46197,7 +46197,7 @@
         <v>235</v>
       </c>
       <c r="C2860" s="2" t="n">
-        <v>232.16</v>
+        <v>232.2</v>
       </c>
       <c r="D2860" s="2" t="n">
         <v>226.24</v>
@@ -46245,7 +46245,7 @@
         <v>819.75</v>
       </c>
       <c r="C2863" s="2" t="n">
-        <v>781.15</v>
+        <v>786.05</v>
       </c>
       <c r="D2863" s="2" t="n">
         <v>736.6</v>
@@ -46597,7 +46597,7 @@
         <v>211</v>
       </c>
       <c r="C2885" s="2" t="n">
-        <v>201.02</v>
+        <v>202.38</v>
       </c>
       <c r="D2885" s="2" t="n">
         <v>191.53</v>
@@ -46661,10 +46661,10 @@
         <v>95.53</v>
       </c>
       <c r="C2889" s="2" t="n">
-        <v>87.59999999999999</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="D2889" s="2" t="n">
-        <v>84.63</v>
+        <v>86.98999999999999</v>
       </c>
     </row>
     <row r="2890">
@@ -46677,7 +46677,7 @@
         <v>873.05</v>
       </c>
       <c r="C2890" s="2" t="n">
-        <v>820.1</v>
+        <v>829</v>
       </c>
       <c r="D2890" s="2" t="n">
         <v>810.2</v>
@@ -47125,10 +47125,10 @@
         <v>90.40000000000001</v>
       </c>
       <c r="C2918" s="2" t="n">
-        <v>83.20999999999999</v>
+        <v>87</v>
       </c>
       <c r="D2918" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="2919">
@@ -47192,7 +47192,7 @@
         <v>3825</v>
       </c>
       <c r="D2922" s="2" t="n">
-        <v>3773</v>
+        <v>3790.6</v>
       </c>
     </row>
     <row r="2923">
@@ -47381,7 +47381,7 @@
         <v>480</v>
       </c>
       <c r="C2934" s="2" t="n">
-        <v>436.25</v>
+        <v>439.9</v>
       </c>
       <c r="D2934" s="2" t="n">
         <v>416.15</v>
@@ -47445,7 +47445,7 @@
         <v>146</v>
       </c>
       <c r="C2938" s="2" t="n">
-        <v>136.47</v>
+        <v>138.69</v>
       </c>
       <c r="D2938" s="2" t="n">
         <v>127.81</v>
@@ -47493,10 +47493,10 @@
         <v>1300</v>
       </c>
       <c r="C2941" s="2" t="n">
-        <v>1251.6</v>
+        <v>1270.4</v>
       </c>
       <c r="D2941" s="2" t="n">
-        <v>1081</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="2942">
